--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XI-XX/FRACC XVI/LTAIPT_A63F16B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XI-XX/FRACC XVI/LTAIPT_A63F16B.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="58">
   <si>
     <t>48965</t>
   </si>
@@ -158,16 +158,16 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>04746DC2EDED56D3B0AECF136787CCCC</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>7035E4F9C32A661BF2650E125BA36B01</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
   </si>
   <si>
     <t/>
@@ -176,19 +176,13 @@
     <t>Departamento de contabilidad</t>
   </si>
   <si>
-    <t>03/01/2023</t>
+    <t>01/04/2023</t>
   </si>
   <si>
     <t>05/04/2018</t>
   </si>
   <si>
-    <t>Durante el período del 01 de octubre de 2022 al 31 de diciembre de 2022,  el Colegio de Bachilleres del Estado de Tlaxcala, no asigna recursos públicos a personas físicas o morales, nacionales y/o extranjeras, incluso a los sindicatos que realicen actos de autoridad bajo designación presupuestal especial y específica o por cualquier otro motivo, apegándose únicamente a los conceptos establecidos en las Condiciones Generales de Trabajo y Contrato Colectivo de Trabajo, en este sentido al no existir información qué publicar, no se ha modificado la fecha de actualización y en su caso establecer un hipervínculo de los programas con objetivos y metas.</t>
-  </si>
-  <si>
-    <t>4266077B675AC1FAD6B9CB52D538748A</t>
-  </si>
-  <si>
-    <t>Durante el período del 01 de octubre de 2022 al 31 de diciembre de 2022,  el Colegio de Bachilleres del Estado de Tlaxcala, no asigna recursos públicos a personas físicas o morales, nacionales y/o extranjeras, incluso a los sindicatos y a las personas físicas o morales que realicen actos de autoridad bajo designación presupuestal especial y específica o por cualquier otro motivo, apegándose únicamente a los conceptos establecidos en las Condiciones Generales de Trabajo y Contrato Colectivo de Trabajo, en este sentido al no existir información qué publicar, no se establece un hipervínculo de los programas con objetivos y metas.</t>
+    <t>Durante el período del 01 de enero de 2023 al 31 de marzo de 2023,  el Colegio de Bachilleres del Estado de Tlaxcala, no asigna recursos públicos a personas físicas o morales, nacionales y/o extranjeras, incluso a los sindicatos que realicen actos de autoridad bajo designación presupuestal especial y específica o por cualquier otro motivo, apegándose únicamente a los conceptos establecidos en las Condiciones Generales de Trabajo y Contrato Colectivo de Trabajo, en este sentido al no existir información qué publicar, no se ha modificado la fecha de actualización y en su caso establecer un hipervínculo de los programas con objetivos y metas.</t>
   </si>
   <si>
     <t>Efectivo</t>
@@ -590,10 +584,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.5703125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.140625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -873,59 +867,6 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A6:Q6"/>
@@ -937,7 +878,7 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E181">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E201">
       <formula1>Hidden_14</formula1>
     </dataValidation>
   </dataValidations>
@@ -952,17 +893,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
